--- a/data/curriculo_unicafam/mig_propuestas/PROP_02_IA_Generativa_y_Arquitect_MIG.xlsx
+++ b/data/curriculo_unicafam/mig_propuestas/PROP_02_IA_Generativa_y_Arquitect_MIG.xlsx
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -182,6 +182,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -548,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H46"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -595,7 +598,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.0 (PENDIENTE_REVISION)</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -612,7 +615,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H3" s="2" t="n"/>
@@ -1210,23 +1213,96 @@
       <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="n"/>
     </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>GOBERNANZA CURRICULAR Y TRAZABILIDAD DE APROBACIÓN (MEN DECRETO 1330)</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="n"/>
+      <c r="C48" s="13" t="n"/>
+      <c r="D48" s="13" t="n"/>
+      <c r="E48" s="13" t="n"/>
+      <c r="F48" s="13" t="n"/>
+      <c r="G48" s="13" t="n"/>
+      <c r="H48" s="13" t="n"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>ESTADO DE APROBACIÓN</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>PENDIENTE_REVISION (Versión v1)</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="n"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>AVAL / DECISIÓN DIRECTIVA</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente de Visto Bueno por Comité Curricular</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="n"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>FECHA ÚLTIMA DECISIÓN</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>En proceso de revisión</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="52">
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="E43:E44"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
+    <mergeCell ref="A48:H48"/>
     <mergeCell ref="B43:B44"/>
     <mergeCell ref="C39:C41"/>
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="C50:H50"/>
+    <mergeCell ref="A49:B49"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="B12:B15"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="C26:H28"/>
+    <mergeCell ref="A51:B51"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="C43:D44"/>
     <mergeCell ref="E39:F41"/>
     <mergeCell ref="C11:H11"/>
+    <mergeCell ref="C51:H51"/>
     <mergeCell ref="D39:D41"/>
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="B26:B28"/>
@@ -1239,11 +1315,13 @@
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="B1:E4"/>
     <mergeCell ref="B37:B38"/>
+    <mergeCell ref="A50:B50"/>
     <mergeCell ref="C29:H32"/>
     <mergeCell ref="G39:G41"/>
     <mergeCell ref="F45:H46"/>
     <mergeCell ref="C22:H25"/>
     <mergeCell ref="E45:E46"/>
+    <mergeCell ref="C49:H49"/>
     <mergeCell ref="B45:B46"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="C6:H6"/>

--- a/data/curriculo_unicafam/mig_propuestas/PROP_02_IA_Generativa_y_Arquitect_MIG.xlsx
+++ b/data/curriculo_unicafam/mig_propuestas/PROP_02_IA_Generativa_y_Arquitect_MIG.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>1.0 (PENDIENTE_REVISION)</t>
+          <t>2.0 (APROBADO)</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -615,7 +615,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="H3" s="2" t="n"/>
@@ -838,7 +838,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>La revolución de la Inteligencia Artificial Generativa y los Modelos de Lenguaje de Gran Escala (LLMs) ha transformado la demanda empresarial. Los egresados de UniCafam cuentan con sólidas competencias en Procesamiento de Lenguaje Natural (NLP) tradicional gracias a la materia 'Procesamiento de Texto y Técnicas de Información'. Esta microcredencial tiende un puente directo hacia las tecnologías más modernas de IA de Frontera: Retrieval-Augmented Generation (RAG) y bases de datos vectoriales. Conectando lo que ya saben de procesamiento de texto con LLMs comerciales y de código abierto (Llama, OpenAI, Claude), el egresado se transforma en un desarrollador de soluciones cognitivas inteligentes que automatizan la búsqueda de información corporativa, impulsando su empleabilidad en un mercado que valora estas competencias en niveles sumamente altos.</t>
+          <t>La revolución de la Inteligencia Artificial Generativa y los Modelos de Lenguaje de Gran Escala (LLMs) está redefiniendo la eficiencia operativa, la automatización del conocimiento y el ROI empresarial. Los profesionales deben trascender el desarrollo conceptual para entregar soluciones de alto valor corporativo orientadas al negocio. Esta microcredencial articula las competencias previas en NLP y análisis de datos de los egresados de UniCafam con arquitecturas de frontera como Retrieval-Augmented Generation (RAG), almacenamiento en bases de datos vectoriales y orquestación cognitiva. El programa enfatiza el caso de negocio real, el cálculo de costo-beneficio de inferencias y la entrega de un producto funcional desplegado en producción cloud (AWS/Azure) y respaldado en GitHub, otorgando una ventaja altamente competitiva y demostrable en entrevistas de trabajo e iniciativas de transformación digital.</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -882,10 +882,10 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>• Objetivo General: Capacitar en el diseño, desarrollo e integración de sistemas de IA Generativa empresariales utilizando arquitecturas RAG para optimizar la toma de decisiones y la automatización de procesos de consulta.
-• Objetivo Específico 1: Utilizar frameworks avanzados de desarrollo (LangChain e Indexadores) para orquestar flujos cognitivos complejos basados en LLMs.
-• Objetivo Específico 2: Implementar bases de datos vectoriales para el almacenamiento de embeddings semánticos optimizados.
-• Objetivo Específico 3: Diseñar aplicaciones web que utilicen técnicas de Prompt Engineering avanzado y agentes inteligentes autónomos.</t>
+          <t>• Objetivo General: Capacitar en el diseño, desarrollo, evaluación de impacto financiero e integración de sistemas de IA Generativa empresariales utilizando arquitecturas RAG para optimizar la toma de decisiones, garantizando el despliegue funcional en entornos de nube y repositorios públicos orientados a portafolios profesionales.
+• Objetivo Específico 1: Evaluar casos de uso de negocio y modelos de orquestación cognitiva (LangChain / LlamaIndex) para resolver ineficiencias operativas con métricas claras de ROI.
+• Objetivo Específico 2: Implementar bases de datos vectoriales en producción para el almacenamiento y recuperación de embeddings semánticos con enfoque en seguridad y costo eficientes.
+• Objetivo Específico 3: Desplegar un Proyecto Integrador de negocio en un servicio de nube pública (AWS o Azure) con código fuente versionado en GitHub para demostración efectiva en procesos de selección y desarrollo profesional.</t>
         </is>
       </c>
       <c r="D22" s="2" t="n"/>
@@ -929,7 +929,7 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Científicos de datos, tecnólogos en análisis de datos, ingenieros de desarrollo de software, analistas de BI senior y entusiastas de la tecnología con nociones lógicas de programación en Python.</t>
+          <t>Científicos de datos, tecnólogos en análisis de datos, ingenieros de desarrollo de software, analistas de BI senior, consultores de innovación y líderes técnicos con nociones lógicas de programación en Python interesados en aplicar IA con impacto real en los negocios.</t>
         </is>
       </c>
       <c r="D26" s="2" t="n"/>
@@ -964,7 +964,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Enfoque de taller práctico hands-on. Cada sesión sincrónica introduce un reto técnico real de la industria (p. ej., construir un chatbot que responda preguntas basadas exclusivamente en los manuales de procedimientos de una empresa). Los laboratorios se desarrollan sobre cuadernos de Jupyter de Google Colab utilizando APIs comerciales y modelos open-source de Hugging Face. Se utiliza un canal continuo de comunicación en Discord para mentorías personalizadas de código.</t>
+          <t>Enfoque 100% práctico ('learning-by-doing') orientado a la resolución de retos de negocio. A lo largo del programa, los participantes desarrollan un Proyecto Integrador de IA Generativa basado en una necesidad empresarial real (ej. asistente financiero de consulta documental, automatizador RAG para áreas normativas o gestor inteligente de servicio al cliente). Las sesiones combinan teoría aplicada, laboratorios en Google Colab con APIs comerciales y modelos open-source, y mentorías dedicadas al versionamiento de código en GitHub y el despliegue continuo en la nube (AWS/Azure). El programa finaliza con un Demo Day donde los estudiantes presentan sus productos desplegados en producción y sus repositorios públicos para exhibir en su portafolio laboral.</t>
         </is>
       </c>
       <c r="D29" s="2" t="n"/>
@@ -1008,9 +1008,11 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>✔ Inclusión en el portafolio institucional de microcredenciales digitales insignias de UniCafam con estándar internacional OpenBadges para compartir en LinkedIn.
-✔ Acceso directo a la comunidad de expertos en Inteligencia Artificial de la escuela de Ingeniería UniCafam.
-✔ Plantillas de código listas para producción en entornos empresariales.</t>
+          <t>✔ Proyecto Final integrador real desplegado en infraestructura Cloud (AWS/Azure) y listo para incluir en el perfil de LinkedIn y portafolio laboral.
+✔ Repositorio funcional en GitHub estructurado bajo estándares de la industria, optimizado para ser presentado como evidencia técnica en entrevistas de trabajo.
+✔ Inclusión en el portafolio institucional de microcredenciales digitales insignias de UniCafam con estándar internacional OpenBadges.
+✔ Acceso directo a la comunidad de expertos en Inteligencia Artificial y Transformación Digital de la Escuela de Ingeniería de UniCafam.
+✔ Plantillas de código y arquitectura orientadas a producción empresarial con estimación de costos operacionales.</t>
         </is>
       </c>
       <c r="D33" s="2" t="n"/>
@@ -1103,19 +1105,19 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Arquitecturas RAG &amp; Bases de Datos Vectoriales</t>
+          <t>Arquitecturas RAG &amp; Bases de Datos Vectoriales para Soluciones de Negocio</t>
         </is>
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>1. Introducción a la IA Generativa, Modelos Fundacionales y Transformers.
-2. Fundamentos de Embeddings: Conversión de texto a vectores densos.
-3. Bases de Datos Vectoriales: Almacenamiento, indexación y búsqueda en Pinecone, ChromaDB y Qdrant.
-4. El flujo RAG (Retrieval-Augmented Generation): Conexión de documentos privados con LLMs.
-5. Frameworks de Orquestación: Construcción paso a paso con LangChain y LlamaIndex.
-6. Prompt Engineering Avanzado, técnicas Few-Shot y control de alucinaciones.
-7. Agentes autónomos de IA que interactúan con APIs externas y SQL corporativo.
-8. Despliegue de un prototipo interactivo utilizando Streamlit. [Stack: LangChain, Pinecone, ChromaDB, OpenAI API, Hugging Face, Streamlit]</t>
+          <t>1. Estrategia de IA Generativa en Negocios: Casos de uso, estimación de ROI, latencia y costos de inferencia por token.
+2. Fundamentos de Embeddings &amp; Búsqueda Semántica aplicados a repositorios documentales corporativos.
+3. Bases de Datos Vectoriales (Pinecone, ChromaDB, Qdrant): Gestión, indexación, particionamiento por tenant y seguridad de datos empresariales.
+4. Flujo RAG (Retrieval-Augmented Generation) Avanzado: Chunking estratégico, re-ranking y reducción de alucinaciones en entornos de negocio.
+5. Frameworks de Orquestación: Construcción paso a paso de flujos cognitivos eficientes con LangChain y LlamaIndex.
+6. Agentes Autónomos y Tool Use: Integración con APIs corporativas y bases de datos SQL para analítica conversacional.
+7. Versionamiento Profesional: Estructuración de proyectos, buenas prácticas de código y documentación en GitHub para portafolio laboral.
+8. Proyecto Final Integrador &amp; Despliegue Cloud: Empaquetamiento de la aplicación (Streamlit/FastAPI) y despliegue continuo en AWS (App Runner/EC2) o Azure (Container Apps/Web Apps) con demostración para entrevistas de trabajo. [Stack: LangChain, LlamaIndex, Pinecone, ChromaDB, OpenAI API / Claude, GitHub, AWS (App Runner / EC2), Azure (Container Apps), Streamlit / FastAPI]</t>
         </is>
       </c>
       <c r="F39" s="2" t="n"/>
@@ -1187,18 +1189,18 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Investigador / Ingeniero Senior en NLP &amp; IA Generativa</t>
+          <t>Investigador / Ingeniero Senior en NLP &amp; IA Generativa para Negocios</t>
         </is>
       </c>
       <c r="D45" s="2" t="n"/>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>Arquitecturas RAG &amp; Bases de Datos Vectoriales</t>
+          <t>Arquitecturas RAG &amp; Bases de Datos Vectoriales para Soluciones de Negocio</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>Profesional en Ingeniería de Sistemas, Inteligencia Artificial o Ciencia de Datos, con Maestría o Doctorado en Inteligencia Artificial o Computación Cognitiva, con publicaciones científicas o experiencia de mínimo 3 años desarrollando productos basados en tecnologías Transformers y modelos GPT.</t>
+          <t>Profesional en Ingeniería de Sistemas, Inteligencia Artificial o Ciencia de Datos, con Maestría o Doctorado en IA, Ciencias de la Computación o Áreas Afines, con más de 3 años de experiencia liderando proyectos de IA Generativa en la industria, despliegue en entornos Cloud (AWS/Azure) y desarrollo de soluciones de impacto de negocio.</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1236,7 +1238,7 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>PENDIENTE_REVISION (Versión v1)</t>
+          <t>APROBADO (Versión v2)</t>
         </is>
       </c>
       <c r="D49" s="2" t="n"/>
@@ -1254,7 +1256,7 @@
       <c r="B50" s="2" t="n"/>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Pendiente de Visto Bueno por Comité Curricular</t>
+          <t>Decanatura / Comité Curricular UniCafam (Usuario Aprobador)</t>
         </is>
       </c>
       <c r="D50" s="2" t="n"/>
@@ -1272,7 +1274,7 @@
       <c r="B51" s="2" t="n"/>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>En proceso de revisión</t>
+          <t>2026-10-24 08:59:15</t>
         </is>
       </c>
       <c r="D51" s="2" t="n"/>

--- a/data/curriculo_unicafam/mig_propuestas/PROP_02_IA_Generativa_y_Arquitect_MIG.xlsx
+++ b/data/curriculo_unicafam/mig_propuestas/PROP_02_IA_Generativa_y_Arquitect_MIG.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>2.0 (APROBADO)</t>
+          <t>3.0 (PENDIENTE_REVISION)</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -615,7 +615,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H3" s="2" t="n"/>
@@ -753,7 +753,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>$1.500.000 COP</t>
+          <t>Por definir según tarifario institucional</t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>$1.125.000 COP (25% dcto)</t>
+          <t>Por definir según tarifario institucional</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>
@@ -787,7 +787,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>$1.200.000 COP (20% dcto)</t>
+          <t>Por definir según tarifario institucional</t>
         </is>
       </c>
       <c r="E14" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>$1.050.000 COP (por convenio empresarial &gt;3 personas)</t>
+          <t>Por definir según tarifario institucional</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -838,7 +838,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>La revolución de la Inteligencia Artificial Generativa y los Modelos de Lenguaje de Gran Escala (LLMs) está redefiniendo la eficiencia operativa, la automatización del conocimiento y el ROI empresarial. Los profesionales deben trascender el desarrollo conceptual para entregar soluciones de alto valor corporativo orientadas al negocio. Esta microcredencial articula las competencias previas en NLP y análisis de datos de los egresados de UniCafam con arquitecturas de frontera como Retrieval-Augmented Generation (RAG), almacenamiento en bases de datos vectoriales y orquestación cognitiva. El programa enfatiza el caso de negocio real, el cálculo de costo-beneficio de inferencias y la entrega de un producto funcional desplegado en producción cloud (AWS/Azure) y respaldado en GitHub, otorgando una ventaja altamente competitiva y demostrable en entrevistas de trabajo e iniciativas de transformación digital.</t>
+          <t>La Inteligencia Artificial Generativa y los Modelos de Lenguaje de Gran Escala (LLMs) están redefiniendo la eficiencia operativa en el sector empresarial. Según el Observatorio de Empleo UniCafam (corte 2026-10-28, n=570 ofertas), Python presenta una alta demanda situándose en un 56.7% de las ofertas (323 ofertas), seguido por habilidades clave como SQL en un 62.3% (355 ofertas) y ETL / Pipelines de Datos en un 45.4% (259 ofertas). Por su parte, la habilidad de NLP / LLMs se encuentra en un 6.1% de las ofertas (35 ofertas), AWS en un 23.5% (134 ofertas) y Azure en un 24.0% (137 ofertas). Esta microcredencial articula las competencias en Python y bases de datos con arquitecturas avanzadas como Retrieval-Augmented Generation (RAG), almacenamiento en bases de datos vectoriales y orquestación cognitiva, permitiendo integrar soluciones desplegadas en servicios cloud y respaldadas en repositorios públicos para fortalecer el portafolio profesional.</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -882,10 +882,10 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>• Objetivo General: Capacitar en el diseño, desarrollo, evaluación de impacto financiero e integración de sistemas de IA Generativa empresariales utilizando arquitecturas RAG para optimizar la toma de decisiones, garantizando el despliegue funcional en entornos de nube y repositorios públicos orientados a portafolios profesionales.
-• Objetivo Específico 1: Evaluar casos de uso de negocio y modelos de orquestación cognitiva (LangChain / LlamaIndex) para resolver ineficiencias operativas con métricas claras de ROI.
-• Objetivo Específico 2: Implementar bases de datos vectoriales en producción para el almacenamiento y recuperación de embeddings semánticos con enfoque en seguridad y costo eficientes.
-• Objetivo Específico 3: Desplegar un Proyecto Integrador de negocio en un servicio de nube pública (AWS o Azure) con código fuente versionado en GitHub para demostración efectiva en procesos de selección y desarrollo profesional.</t>
+          <t>• Objetivo General: Capacitar en el diseño, desarrollo, evaluación de impacto y despliegue de sistemas de IA Generativa empresariales utilizando arquitecturas RAG para optimizar la toma de decisiones, garantizando el despliegue funcional en entornos de nube y repositorios públicos orientados a portafolios profesionales.
+• Objetivo Específico 1: Evaluar casos de uso de negocio y modelos de orquestación cognitiva (LangChain / LlamaIndex) para resolver ineficiencias operativas con métricas claras de viabilidad técnica y financiera.
+• Objetivo Específico 2: Implementar bases de datos vectoriales para el almacenamiento y recuperación de embeddings semánticos con enfoque en seguridad y eficiencia.
+• Objetivo Específico 3: Desplegar un Proyecto Integrador de negocio en un servicio de nube pública (AWS o Azure) con código fuente versionado en GitHub para su demostración en portafolios profesionales.</t>
         </is>
       </c>
       <c r="D22" s="2" t="n"/>
@@ -929,7 +929,7 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Científicos de datos, tecnólogos en análisis de datos, ingenieros de desarrollo de software, analistas de BI senior, consultores de innovación y líderes técnicos con nociones lógicas de programación en Python interesados en aplicar IA con impacto real en los negocios.</t>
+          <t>Científicos de datos, tecnólogos en análisis de datos, ingenieros de desarrollo de software, analistas de BI senior, consultores de innovación y líderes técnicos con conocimientos en programación con Python interesados en aplicar IA con impacto real en los negocios.</t>
         </is>
       </c>
       <c r="D26" s="2" t="n"/>
@@ -964,7 +964,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Enfoque 100% práctico ('learning-by-doing') orientado a la resolución de retos de negocio. A lo largo del programa, los participantes desarrollan un Proyecto Integrador de IA Generativa basado en una necesidad empresarial real (ej. asistente financiero de consulta documental, automatizador RAG para áreas normativas o gestor inteligente de servicio al cliente). Las sesiones combinan teoría aplicada, laboratorios en Google Colab con APIs comerciales y modelos open-source, y mentorías dedicadas al versionamiento de código en GitHub y el despliegue continuo en la nube (AWS/Azure). El programa finaliza con un Demo Day donde los estudiantes presentan sus productos desplegados en producción y sus repositorios públicos para exhibir en su portafolio laboral.</t>
+          <t>Enfoque 100% práctico ('learning-by-doing') orientado a la resolución de retos de negocio. A lo largo del programa, los participantes desarrollan un Proyecto Integrador de IA Generativa basado en una necesidad empresarial real. Las sesiones combinan teoría aplicada, laboratorios en Google Colab con APIs comerciales y modelos open-source, y mentorías dedicadas al versionamiento de código en GitHub y el despliegue continuo en la nube (AWS/Azure). El programa finaliza con un Demo Day donde los estudiantes presentan sus productos desplegados en producción y sus repositorios públicos.</t>
         </is>
       </c>
       <c r="D29" s="2" t="n"/>
@@ -1008,10 +1008,10 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>✔ Proyecto Final integrador real desplegado en infraestructura Cloud (AWS/Azure) y listo para incluir en el perfil de LinkedIn y portafolio laboral.
-✔ Repositorio funcional en GitHub estructurado bajo estándares de la industria, optimizado para ser presentado como evidencia técnica en entrevistas de trabajo.
+          <t>✔ Proyecto Final integrador real desplegado en infraestructura Cloud (AWS/Azure) listo para incluir en el perfil profesional.
+✔ Repositorio funcional en GitHub estructurado bajo estándares de la industria, optimizado como evidencia técnica.
 ✔ Inclusión en el portafolio institucional de microcredenciales digitales insignias de UniCafam con estándar internacional OpenBadges.
-✔ Acceso directo a la comunidad de expertos en Inteligencia Artificial y Transformación Digital de la Escuela de Ingeniería de UniCafam.
+✔ Acceso a la comunidad de expertos en Inteligencia Artificial y Transformación Digital de la Escuela de Ingeniería de UniCafam.
 ✔ Plantillas de código y arquitectura orientadas a producción empresarial con estimación de costos operacionales.</t>
         </is>
       </c>
@@ -1110,14 +1110,14 @@
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>1. Estrategia de IA Generativa en Negocios: Casos de uso, estimación de ROI, latencia y costos de inferencia por token.
+          <t>1. Estrategia de IA Generativa en Negocios: Casos de uso, estimación de viabilidad, latencia y costos de inferencia por token.
 2. Fundamentos de Embeddings &amp; Búsqueda Semántica aplicados a repositorios documentales corporativos.
-3. Bases de Datos Vectoriales (Pinecone, ChromaDB, Qdrant): Gestión, indexación, particionamiento por tenant y seguridad de datos empresariales.
-4. Flujo RAG (Retrieval-Augmented Generation) Avanzado: Chunking estratégico, re-ranking y reducción de alucinaciones en entornos de negocio.
-5. Frameworks de Orquestación: Construcción paso a paso de flujos cognitivos eficientes con LangChain y LlamaIndex.
+3. Bases de Datos Vectoriales (Pinecone, ChromaDB, Qdrant): Gestión, indexación y seguridad de datos empresariales.
+4. Flujo RAG (Retrieval-Augmented Generation) Avanzado: Chunking estratégico, re-ranking y mitigación de alucinaciones.
+5. Frameworks de Orquestación: Construcción paso a paso de flujos cognitivos con LangChain y LlamaIndex.
 6. Agentes Autónomos y Tool Use: Integración con APIs corporativas y bases de datos SQL para analítica conversacional.
-7. Versionamiento Profesional: Estructuración de proyectos, buenas prácticas de código y documentación en GitHub para portafolio laboral.
-8. Proyecto Final Integrador &amp; Despliegue Cloud: Empaquetamiento de la aplicación (Streamlit/FastAPI) y despliegue continuo en AWS (App Runner/EC2) o Azure (Container Apps/Web Apps) con demostración para entrevistas de trabajo. [Stack: LangChain, LlamaIndex, Pinecone, ChromaDB, OpenAI API / Claude, GitHub, AWS (App Runner / EC2), Azure (Container Apps), Streamlit / FastAPI]</t>
+7. Versionamiento Profesional con Git/GitHub: Estructuración de proyectos y documentación de código.
+8. Proyecto Final Integrador &amp; Despliegue Cloud: Empaquetamiento de la aplicación y despliegue en servicios de nube (AWS o Azure) para portafolio laboral. [Stack: Python, SQL, LangChain, LlamaIndex, Pinecone, ChromaDB, OpenAI API / Claude, Git / GitHub, AWS, Azure, Streamlit / FastAPI]</t>
         </is>
       </c>
       <c r="F39" s="2" t="n"/>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>Profesional en Ingeniería de Sistemas, Inteligencia Artificial o Ciencia de Datos, con Maestría o Doctorado en IA, Ciencias de la Computación o Áreas Afines, con más de 3 años de experiencia liderando proyectos de IA Generativa en la industria, despliegue en entornos Cloud (AWS/Azure) y desarrollo de soluciones de impacto de negocio.</t>
+          <t>Profesional en Ingeniería de Sistemas, Inteligencia Artificial o Ciencia de Datos, con Posgrado o experiencia equivalente en IA y Ciencias de la Computación, con más de 3 años de experiencia liderando proyectos de IA Generativa en la industria, despliegue en entornos Cloud (AWS/Azure) y desarrollo de soluciones de datos.</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1215,6 +1215,7 @@
       <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="n"/>
     </row>
+    <row r="47"/>
     <row r="48" ht="24" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
         <is>
@@ -1238,7 +1239,7 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>APROBADO (Versión v2)</t>
+          <t>PENDIENTE_REVISION (Versión v3)</t>
         </is>
       </c>
       <c r="D49" s="2" t="n"/>
@@ -1256,7 +1257,7 @@
       <c r="B50" s="2" t="n"/>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Decanatura / Comité Curricular UniCafam (Usuario Aprobador)</t>
+          <t>Pendiente de Visto Bueno por Comité Curricular</t>
         </is>
       </c>
       <c r="D50" s="2" t="n"/>
@@ -1274,7 +1275,7 @@
       <c r="B51" s="2" t="n"/>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>2026-10-24 08:59:15</t>
+          <t>2026-10-28 01:42:38</t>
         </is>
       </c>
       <c r="D51" s="2" t="n"/>

--- a/data/curriculo_unicafam/mig_propuestas/PROP_02_IA_Generativa_y_Arquitect_MIG.xlsx
+++ b/data/curriculo_unicafam/mig_propuestas/PROP_02_IA_Generativa_y_Arquitect_MIG.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>3.0 (PENDIENTE_REVISION)</t>
+          <t>4.0 (PENDIENTE_REVISION)</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -615,7 +615,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H3" s="2" t="n"/>
@@ -838,7 +838,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>La Inteligencia Artificial Generativa y los Modelos de Lenguaje de Gran Escala (LLMs) están redefiniendo la eficiencia operativa en el sector empresarial. Según el Observatorio de Empleo UniCafam (corte 2026-10-28, n=570 ofertas), Python presenta una alta demanda situándose en un 56.7% de las ofertas (323 ofertas), seguido por habilidades clave como SQL en un 62.3% (355 ofertas) y ETL / Pipelines de Datos en un 45.4% (259 ofertas). Por su parte, la habilidad de NLP / LLMs se encuentra en un 6.1% de las ofertas (35 ofertas), AWS en un 23.5% (134 ofertas) y Azure en un 24.0% (137 ofertas). Esta microcredencial articula las competencias en Python y bases de datos con arquitecturas avanzadas como Retrieval-Augmented Generation (RAG), almacenamiento en bases de datos vectoriales y orquestación cognitiva, permitiendo integrar soluciones desplegadas en servicios cloud y respaldadas en repositorios públicos para fortalecer el portafolio profesional.</t>
+          <t>La Inteligencia Artificial Generativa y los Modelos de Lenguaje de Gran Escala (LLMs) están redefiniendo la eficiencia operativa en el sector empresarial. Según el Observatorio de Empleo UniCafam (corte 2026-10-28, n=570 ofertas), Python presenta una alta demanda situándose en un 56.7% de las ofertas (323 ofertas), seguido por habilidades clave como SQL en un 62.3% (355 ofertas) y ETL / Pipelines de Datos en un 45.4% (259 ofertas). Por su parte, la habilidad de NLP / LLMs se encuentra en un 6.1% de las ofertas (35 ofertas), AWS en un 23.5% (134 ofertas), Azure en un 24.0% (137 ofertas) y Git / Control de Versiones en un 14.6% (83 ofertas). Esta microcredencial articula las competencias en Python y bases de datos con arquitecturas avanzadas como Retrieval-Augmented Generation (RAG), almacenamiento en bases de datos vectoriales y orquestación cognitiva, permitiendo integrar soluciones desplegadas en servicios cloud y respaldadas en repositorios públicos para fortalecer el portafolio profesional.</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -1239,7 +1239,7 @@
       <c r="B49" s="2" t="n"/>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>PENDIENTE_REVISION (Versión v3)</t>
+          <t>PENDIENTE_REVISION (Versión v4)</t>
         </is>
       </c>
       <c r="D49" s="2" t="n"/>
@@ -1275,7 +1275,7 @@
       <c r="B51" s="2" t="n"/>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>2026-10-28 01:42:38</t>
+          <t>2026-10-29 01:19:16</t>
         </is>
       </c>
       <c r="D51" s="2" t="n"/>
